--- a/Operation-Snackstorm/Assets/Qa/Operation_TestCase_0.001mm.xlsx
+++ b/Operation-Snackstorm/Assets/Qa/Operation_TestCase_0.001mm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3-2\Operation-Snackstorm\Operation-Snackstorm\Assets\Qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2429343-2DC8-43B4-893A-7F705DEFBA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FB10F1-D405-4727-9E1A-B2A28DA8B08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1485" windowWidth="26865" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCase" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="306">
   <si>
     <t>No</t>
   </si>
@@ -1549,22 +1549,6 @@
   </si>
   <si>
     <r>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>라운드</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="9"/>
         <rFont val="맑은 고딕"/>
@@ -2896,6 +2880,14 @@
   </si>
   <si>
     <t>안정적</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3라운드</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -3072,7 +3064,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3193,6 +3185,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3249,16 +3250,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3300,9 +3295,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3327,18 +3319,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3351,21 +3331,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3373,12 +3338,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3393,6 +3352,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3405,2720 +3370,47 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="310">
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -6253,310 +3545,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFEFEFEF"/>
           <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE5CD"/>
-          <bgColor rgb="FFFCE5CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9900FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0000FF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7018,7 +4006,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -7057,10 +4045,10 @@
         <f t="shared" ref="A2:A49" si="0">ROW()-2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -7073,14 +4061,14 @@
       <c r="G2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>47</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="24" t="s">
-        <v>257</v>
+      <c r="J2" s="22" t="s">
+        <v>256</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>14</v>
@@ -7092,65 +4080,65 @@
     </row>
     <row r="3" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="22" t="s">
         <v>45</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="22" t="s">
         <v>48</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="K3" s="42" t="s">
-        <v>266</v>
+      <c r="J3" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="K3" s="39" t="s">
+        <v>265</v>
       </c>
       <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="61" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="47" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>49</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="34" t="s">
         <v>126</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="K4" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>258</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>257</v>
       </c>
       <c r="L4" s="6" t="str">
         <f>IF(B5="",L2,B5)</f>
@@ -7162,29 +4150,29 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="63"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="49"/>
       <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="24" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="34" t="s">
         <v>125</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J5" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="K5" s="34" t="s">
         <v>259</v>
-      </c>
-      <c r="K5" s="37" t="s">
-        <v>260</v>
       </c>
       <c r="L5" s="6" t="str">
         <f>IF(B6="",L4,B6)</f>
@@ -7196,9 +4184,9 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="61" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="47" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -7208,7 +4196,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>25</v>
@@ -7216,11 +4204,11 @@
       <c r="I6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="K6" s="34" t="s">
         <v>261</v>
-      </c>
-      <c r="K6" s="37" t="s">
-        <v>262</v>
       </c>
       <c r="L6" s="6" t="str">
         <f>IF(B7="",L5,B7)</f>
@@ -7232,9 +4220,9 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
       <c r="E7" s="7" t="s">
         <v>27</v>
       </c>
@@ -7250,11 +4238,11 @@
       <c r="I7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="J7" s="34" t="s">
         <v>262</v>
+      </c>
+      <c r="K7" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L7" s="6" t="str">
         <f>IF(B9="",L6,B9)</f>
@@ -7263,9 +4251,9 @@
     </row>
     <row r="8" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="29" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="27" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -7273,7 +4261,7 @@
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>30</v>
@@ -7281,11 +4269,11 @@
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="K8" s="37" t="s">
-        <v>262</v>
+      <c r="J8" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L8" s="6"/>
     </row>
@@ -7294,17 +4282,17 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="63"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="26" t="s">
         <v>51</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="36" t="s">
-        <v>256</v>
+      <c r="G9" s="33" t="s">
+        <v>255</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>30</v>
@@ -7312,11 +4300,11 @@
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="K9" s="37" t="s">
-        <v>262</v>
+      <c r="J9" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L9" s="6" t="str">
         <f>IF(B10="",L7,B10)</f>
@@ -7328,29 +4316,29 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19" t="s">
+      <c r="B10" s="46"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="29" t="s">
         <v>59</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="H10" s="35" t="s">
         <v>127</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>262</v>
+      <c r="J10" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="K10" s="35" t="s">
+        <v>261</v>
       </c>
       <c r="L10" s="6" t="str">
         <f>IF(B11="",L9,B11)</f>
@@ -7362,35 +4350,35 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="34" t="s">
         <v>95</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="24" t="s">
         <v>129</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="K11" s="37" t="s">
-        <v>262</v>
+      <c r="J11" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L11" s="6" t="str">
         <f>IF(B12="",L10,B12)</f>
@@ -7402,31 +4390,31 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="19" t="s">
+      <c r="B12" s="52"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="34" t="s">
         <v>96</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="34" t="s">
         <v>128</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="K12" s="37" t="s">
-        <v>262</v>
+      <c r="J12" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L12" s="6" t="str">
         <f>IF(B13="",L11,B13)</f>
@@ -7438,29 +4426,29 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="19" t="s">
+      <c r="B13" s="52"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="29" t="s">
         <v>93</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="34" t="s">
         <v>130</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="K13" s="34" t="s">
         <v>270</v>
-      </c>
-      <c r="K13" s="37" t="s">
-        <v>271</v>
       </c>
       <c r="L13" s="6" t="str">
         <f>IF(B14="",L12,B14)</f>
@@ -7472,35 +4460,35 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="32" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="34" t="s">
         <v>97</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="34" t="s">
         <v>131</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="L14" s="6" t="e">
-        <f>IF(#REF!="",L13,#REF!)</f>
-        <v>#REF!</v>
+      <c r="J14" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="K14" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="L14" s="6" t="str">
+        <f>IF(B15="",L13,B15)</f>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7508,37 +4496,37 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="34" t="s">
         <v>98</v>
       </c>
       <c r="G15" s="8"/>
-      <c r="H15" s="38" t="s">
+      <c r="H15" s="35" t="s">
         <v>132</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="K15" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L15" s="6" t="e">
-        <f>IF(B16="",#REF!,B16)</f>
-        <v>#REF!</v>
+      <c r="J15" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="K15" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L15" s="6" t="str">
+        <f>IF(B16="",L14,B16)</f>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7546,35 +4534,35 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="56" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="28" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="34" t="s">
         <v>133</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L16" s="6" t="e">
+        <v>272</v>
+      </c>
+      <c r="K16" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L16" s="6" t="str">
         <f>IF(B17="",L15,B17)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7582,10 +4570,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="31" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="29" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="8" t="s">
@@ -7594,21 +4582,21 @@
       <c r="G17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="35" t="s">
         <v>134</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="K17" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L17" s="6" t="e">
+      <c r="J17" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="K17" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L17" s="6" t="str">
         <f>IF(B18="",L16,B18)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7616,33 +4604,33 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="56" t="s">
+      <c r="B18" s="45"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="29" t="s">
         <v>65</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="37" t="s">
+      <c r="H18" s="34" t="s">
         <v>135</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="K18" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L18" s="6" t="e">
+      <c r="J18" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="K18" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L18" s="6" t="str">
         <f>IF(B19="",L17,B19)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7650,41 +4638,41 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="31" t="s">
+      <c r="B19" s="45"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="29" t="s">
         <v>66</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="34" t="s">
         <v>135</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="37" t="s">
+      <c r="J19" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="K19" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="K19" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L19" s="6" t="e">
+      <c r="L19" s="6" t="str">
         <f>IF(B21="",L18,B21)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="56" t="s">
+      <c r="B20" s="45"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="29" t="s">
         <v>86</v>
       </c>
       <c r="F20" s="8"/>
@@ -7698,10 +4686,10 @@
         <v>13</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="K20" s="37" t="s">
-        <v>262</v>
+        <v>278</v>
+      </c>
+      <c r="K20" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L20" s="6"/>
     </row>
@@ -7710,31 +4698,31 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="31" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="38"/>
-      <c r="G21" s="36" t="s">
+      <c r="F21" s="35"/>
+      <c r="G21" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="37" t="s">
         <v>137</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L21" s="6" t="e">
+      <c r="J21" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="K21" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L21" s="6" t="str">
         <f>IF(B22="",L19,B22)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7742,35 +4730,35 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="56" t="s">
+      <c r="B22" s="45"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="36" t="s">
         <v>99</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H22" s="37" t="s">
+      <c r="H22" s="34" t="s">
         <v>138</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="K22" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L22" s="6" t="e">
+      <c r="J22" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="K22" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="L22" s="6" t="str">
         <f>IF(B23="",L21,B23)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7778,31 +4766,31 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="31" t="s">
+      <c r="B23" s="45"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="29" t="s">
         <v>69</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="38" t="s">
+      <c r="H23" s="35" t="s">
         <v>139</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="K23" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L23" s="6" t="e">
+        <v>252</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="K23" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="L23" s="6" t="str">
         <f>IF(B24="",L22,B24)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7810,33 +4798,33 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="56" t="s">
+      <c r="B24" s="45"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="29" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L24" s="6" t="e">
+      <c r="J24" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K24" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="L24" s="6" t="str">
         <f>IF(B25="",L23,B25)</f>
-        <v>#REF!</v>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7844,31 +4832,31 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="31" t="s">
+      <c r="B25" s="45"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="29" t="s">
         <v>71</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="37" t="s">
         <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J25" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L25" s="6" t="e">
-        <f>IF(#REF!="",L24,#REF!)</f>
-        <v>#REF!</v>
+      <c r="J25" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="L25" s="6" t="str">
+        <f>IF(B26="",L24,B26)</f>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7876,29 +4864,29 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="35" t="s">
+      <c r="B26" s="45"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="29" t="s">
         <v>72</v>
       </c>
       <c r="F26" s="8"/>
-      <c r="G26" s="42" t="s">
+      <c r="G26" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="H26" s="37" t="s">
+      <c r="H26" s="34" t="s">
         <v>149</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J26" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>262</v>
+      <c r="J26" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="K26" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L26" s="6" t="e">
         <f>IF(B27="",#REF!,B27)</f>
@@ -7910,29 +4898,29 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="57"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="35" t="s">
+      <c r="B27" s="45"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="28" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="8"/>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="37" t="s">
+      <c r="H27" s="34" t="s">
         <v>125</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>278</v>
+      <c r="J27" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="K27" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L27" s="6" t="e">
         <f>IF(B28="",L26,B28)</f>
@@ -7944,29 +4932,29 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="57" t="s">
+      <c r="B28" s="45"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="31" t="s">
         <v>74</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="34" t="s">
         <v>142</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>262</v>
+        <v>284</v>
+      </c>
+      <c r="K28" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L28" s="6" t="e">
         <f>IF(B29="",L27,B29)</f>
@@ -7978,26 +4966,26 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="36" t="s">
+      <c r="B29" s="45"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="33" t="s">
         <v>84</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="H29" s="41" t="s">
+      <c r="H29" s="38" t="s">
         <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="K29" s="42" t="s">
-        <v>262</v>
+      <c r="J29" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="K29" s="39" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8005,26 +4993,26 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="58"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="46"/>
       <c r="E30" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="36" t="s">
+      <c r="G30" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="42" t="s">
+      <c r="H30" s="39" t="s">
         <v>144</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>278</v>
+      <c r="J30" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="K30" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L30" s="6">
         <f>IF(B30="",L29,B30)</f>
@@ -8033,10 +5021,14 @@
     </row>
     <row r="31" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="30" t="s">
+      <c r="B31" s="45"/>
+      <c r="C31" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="28" t="s">
         <v>113</v>
       </c>
       <c r="F31" s="8" t="s">
@@ -8045,28 +5037,29 @@
       <c r="G31" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="38" t="s">
+      <c r="H31" s="35" t="s">
         <v>145</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J31" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="K31" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L31" s="6"/>
+      <c r="J31" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="K31" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L31" s="6">
+        <f>IF(B32="",L30,B32)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
-      <c r="B32" s="57"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="30" t="s">
+      <c r="B32" s="45"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="28" t="s">
         <v>124</v>
       </c>
       <c r="F32" s="8" t="s">
@@ -8075,50 +5068,51 @@
       <c r="G32" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="H32" s="37" t="s">
+      <c r="H32" s="34" t="s">
         <v>146</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J32" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L32" s="6"/>
+      <c r="J32" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="K32" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="L32" s="6">
+        <f>IF(B33="",L31,B33)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="21" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="31" t="s">
+      <c r="E33" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="34" t="s">
         <v>98</v>
       </c>
       <c r="G33" s="8"/>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="35" t="s">
         <v>132</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J33" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>262</v>
+      <c r="J33" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="K33" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L33" s="6" t="e">
         <f>IF(B34="",#REF!,B34)</f>
@@ -8130,31 +5124,31 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="57"/>
-      <c r="C34" s="66"/>
-      <c r="D34" s="56" t="s">
+      <c r="B34" s="45"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="28" t="s">
         <v>63</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="G34" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H34" s="34" t="s">
         <v>133</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K34" s="37" t="s">
-        <v>262</v>
+        <v>272</v>
+      </c>
+      <c r="K34" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L34" s="6" t="e">
         <f>IF(B35="",L33,B35)</f>
@@ -8166,10 +5160,10 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="57"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="31" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="29" t="s">
         <v>64</v>
       </c>
       <c r="F35" s="8" t="s">
@@ -8178,17 +5172,17 @@
       <c r="G35" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H35" s="38" t="s">
+      <c r="H35" s="35" t="s">
         <v>134</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J35" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>262</v>
+      <c r="J35" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="K35" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L35" s="6" t="e">
         <f>IF(B36="",L34,B36)</f>
@@ -8200,29 +5194,29 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="56" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="E36" s="31" t="s">
+      <c r="E36" s="29" t="s">
         <v>65</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H36" s="37" t="s">
+      <c r="H36" s="34" t="s">
         <v>135</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>262</v>
+      <c r="J36" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="K36" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L36" s="6" t="e">
         <f>IF(B37="",L35,B37)</f>
@@ -8234,27 +5228,27 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="57"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="31" t="s">
+      <c r="B37" s="45"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="29" t="s">
         <v>66</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="37" t="s">
+      <c r="H37" s="34" t="s">
         <v>135</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J37" s="37" t="s">
+      <c r="J37" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="K37" s="34" t="s">
         <v>277</v>
-      </c>
-      <c r="K37" s="37" t="s">
-        <v>278</v>
       </c>
       <c r="L37" s="6" t="e">
         <f>IF(B39="",L36,B39)</f>
@@ -8266,12 +5260,12 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="56" t="s">
+      <c r="B38" s="45"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="31" t="s">
+      <c r="E38" s="29" t="s">
         <v>86</v>
       </c>
       <c r="F38" s="8"/>
@@ -8285,39 +5279,42 @@
         <v>13</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L38" s="6"/>
+        <v>278</v>
+      </c>
+      <c r="K38" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L38" s="6" t="e">
+        <f>IF(B39="",L37,B39)</f>
+        <v>#REF!</v>
+      </c>
     </row>
     <row r="39" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="31" t="s">
+      <c r="B39" s="45"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="38"/>
-      <c r="G39" s="36" t="s">
+      <c r="F39" s="35"/>
+      <c r="G39" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H39" s="40" t="s">
+      <c r="H39" s="37" t="s">
         <v>137</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J39" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>262</v>
+      <c r="J39" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="K39" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L39" s="6" t="e">
         <f>IF(B40="",L37,B40)</f>
@@ -8329,31 +5326,31 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="57"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="56" t="s">
+      <c r="B40" s="45"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="36" t="s">
         <v>99</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H40" s="37" t="s">
+      <c r="H40" s="34" t="s">
         <v>138</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J40" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="37" t="s">
-        <v>278</v>
+      <c r="J40" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="K40" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L40" s="6" t="e">
         <f>IF(B41="",L39,B41)</f>
@@ -8365,27 +5362,27 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="31" t="s">
+      <c r="B41" s="45"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="29" t="s">
         <v>69</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="H41" s="38" t="s">
+      <c r="H41" s="35" t="s">
         <v>139</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="K41" s="37" t="s">
-        <v>278</v>
+        <v>252</v>
+      </c>
+      <c r="J41" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="K41" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L41" s="6" t="e">
         <f>IF(B42="",L40,B42)</f>
@@ -8397,29 +5394,29 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="66"/>
-      <c r="D42" s="56" t="s">
+      <c r="B42" s="45"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="29" t="s">
         <v>70</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H42" s="40" t="s">
+      <c r="H42" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J42" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K42" s="37" t="s">
-        <v>278</v>
+      <c r="J42" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K42" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L42" s="6" t="e">
         <f>IF(B43="",L41,B43)</f>
@@ -8431,27 +5428,27 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="66"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="31" t="s">
+      <c r="B43" s="45"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="29" t="s">
         <v>71</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="H43" s="40" t="s">
+      <c r="H43" s="37" t="s">
         <v>141</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J43" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K43" s="37" t="s">
-        <v>278</v>
+      <c r="J43" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K43" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L43" s="6" t="e">
         <f>IF(#REF!="",L42,#REF!)</f>
@@ -8463,31 +5460,31 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44" s="57"/>
-      <c r="C44" s="66"/>
-      <c r="D44" s="35" t="s">
+      <c r="B44" s="45"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E44" s="31" t="s">
+      <c r="E44" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="F44" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G44" s="42" t="s">
+      <c r="F44" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="G44" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="H44" s="37" t="s">
+      <c r="H44" s="34" t="s">
         <v>149</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J44" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="K44" s="37" t="s">
-        <v>262</v>
+      <c r="J44" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="K44" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L44" s="6" t="e">
         <f>IF(B45="",#REF!,B45)</f>
@@ -8499,29 +5496,29 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="57"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="35" t="s">
+      <c r="B45" s="45"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="30" t="s">
+      <c r="E45" s="28" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="8"/>
-      <c r="G45" s="37" t="s">
+      <c r="G45" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="H45" s="37" t="s">
+      <c r="H45" s="34" t="s">
         <v>125</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J45" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="K45" s="37" t="s">
-        <v>278</v>
+      <c r="J45" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="K45" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L45" s="6" t="e">
         <f>IF(B46="",L44,B46)</f>
@@ -8533,29 +5530,29 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="57"/>
-      <c r="C46" s="66"/>
-      <c r="D46" s="57" t="s">
+      <c r="B46" s="45"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="33" t="s">
+      <c r="E46" s="31" t="s">
         <v>74</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H46" s="37" t="s">
+      <c r="H46" s="34" t="s">
         <v>142</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K46" s="37" t="s">
-        <v>262</v>
+        <v>284</v>
+      </c>
+      <c r="K46" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L46" s="6" t="e">
         <f>IF(B47="",L45,B47)</f>
@@ -8567,26 +5564,30 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="57"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="36" t="s">
+      <c r="B47" s="45"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="33" t="s">
         <v>84</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="H47" s="41" t="s">
+      <c r="H47" s="38" t="s">
         <v>143</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J47" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="K47" s="42" t="s">
-        <v>262</v>
+      <c r="J47" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="K47" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="L47" s="6" t="e">
+        <f>IF(B48="",L46,B48)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8594,62 +5595,64 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="57"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="58"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="46"/>
       <c r="E48" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G48" s="36" t="s">
+      <c r="G48" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="H48" s="42" t="s">
+      <c r="H48" s="39" t="s">
         <v>144</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J48" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="K48" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="L48" s="6">
-        <f>IF(B48="",L47,B48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J48" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="K48" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="L48" s="6" t="e">
+        <f>IF(B49="",L47,B49)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="57"/>
-      <c r="C49" s="46" t="s">
+      <c r="B49" s="45"/>
+      <c r="C49" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="D49" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F49" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="F49" s="26" t="s">
-        <v>151</v>
-      </c>
       <c r="G49" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="H49" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="35" t="s">
         <v>145</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J49" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="K49" s="37" t="s">
-        <v>262</v>
+      <c r="J49" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="K49" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L49" s="6" t="e">
         <f>IF(B50="",#REF!,B50)</f>
@@ -8658,68 +5661,66 @@
     </row>
     <row r="50" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <f t="shared" ref="A50:A64" si="1">ROW()-2</f>
+        <f t="shared" ref="A50:A90" si="1">ROW()-2</f>
         <v>48</v>
       </c>
-      <c r="B50" s="57"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="E50" s="30" t="s">
+      <c r="B50" s="45"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="28" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="H50" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="34" t="s">
         <v>146</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J50" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="K50" s="37" t="s">
-        <v>278</v>
+      <c r="J50" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="K50" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L50" s="6" t="e">
         <f>IF(B51="",L49,B51)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B51" s="57"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="21" t="s">
+      <c r="B51" s="45"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="31" t="s">
+      <c r="E51" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="F51" s="34" t="s">
         <v>98</v>
       </c>
       <c r="G51" s="8"/>
-      <c r="H51" s="38" t="s">
+      <c r="H51" s="35" t="s">
         <v>132</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J51" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="K51" s="37" t="s">
-        <v>262</v>
+      <c r="J51" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="K51" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L51" s="6" t="e">
         <f>IF(B52="",L50,B52)</f>
@@ -8731,31 +5732,31 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B52" s="57"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="56" t="s">
+      <c r="B52" s="45"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="28" t="s">
         <v>63</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G52" s="37" t="s">
+      <c r="G52" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="H52" s="37" t="s">
+      <c r="H52" s="34" t="s">
         <v>133</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K52" s="37" t="s">
-        <v>262</v>
+        <v>272</v>
+      </c>
+      <c r="K52" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L52" s="6" t="e">
         <f>IF(B53="",L51,B53)</f>
@@ -8767,10 +5768,10 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B53" s="57"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="31" t="s">
+      <c r="B53" s="45"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="29" t="s">
         <v>64</v>
       </c>
       <c r="F53" s="8" t="s">
@@ -8779,17 +5780,17 @@
       <c r="G53" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="H53" s="38" t="s">
+      <c r="H53" s="35" t="s">
         <v>134</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J53" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="K53" s="37" t="s">
-        <v>262</v>
+      <c r="J53" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="K53" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L53" s="6" t="e">
         <f>IF(B55="",L52,B55)</f>
@@ -8801,29 +5802,29 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B54" s="57"/>
-      <c r="C54" s="44"/>
-      <c r="D54" s="56" t="s">
+      <c r="B54" s="45"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="29" t="s">
         <v>65</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H54" s="37" t="s">
+      <c r="H54" s="34" t="s">
         <v>135</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J54" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="K54" s="37" t="s">
-        <v>262</v>
+      <c r="J54" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="K54" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L54" s="6"/>
     </row>
@@ -8832,27 +5833,27 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B55" s="57"/>
-      <c r="C55" s="44"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="31" t="s">
+      <c r="B55" s="45"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="29" t="s">
         <v>66</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="H55" s="37" t="s">
+      <c r="H55" s="34" t="s">
         <v>135</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J55" s="37" t="s">
+      <c r="J55" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="K55" s="34" t="s">
         <v>277</v>
-      </c>
-      <c r="K55" s="37" t="s">
-        <v>278</v>
       </c>
       <c r="L55" s="6" t="e">
         <f>IF(B56="",L53,B56)</f>
@@ -8864,12 +5865,12 @@
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B56" s="57"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="56" t="s">
+      <c r="B56" s="45"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="E56" s="29" t="s">
         <v>86</v>
       </c>
       <c r="F56" s="8"/>
@@ -8883,10 +5884,10 @@
         <v>13</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>262</v>
+        <v>278</v>
+      </c>
+      <c r="K56" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L56" s="6" t="e">
         <f>IF(B57="",L55,B57)</f>
@@ -8898,27 +5899,27 @@
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="B57" s="57"/>
-      <c r="C57" s="44"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="31" t="s">
+      <c r="B57" s="45"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="38"/>
-      <c r="G57" s="36" t="s">
+      <c r="F57" s="35"/>
+      <c r="G57" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H57" s="40" t="s">
+      <c r="H57" s="37" t="s">
         <v>137</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J57" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="K57" s="37" t="s">
-        <v>262</v>
+      <c r="J57" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="K57" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L57" s="6" t="e">
         <f>IF(B58="",L56,B58)</f>
@@ -8930,31 +5931,31 @@
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="B58" s="57"/>
-      <c r="C58" s="44"/>
-      <c r="D58" s="56" t="s">
+      <c r="B58" s="45"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E58" s="30" t="s">
+      <c r="E58" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="36" t="s">
         <v>99</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H58" s="37" t="s">
+      <c r="H58" s="34" t="s">
         <v>138</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J58" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="K58" s="37" t="s">
-        <v>278</v>
+      <c r="J58" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="K58" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L58" s="6" t="e">
         <f>IF(B59="",L57,B59)</f>
@@ -8966,27 +5967,27 @@
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B59" s="57"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="31" t="s">
+      <c r="B59" s="45"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="29" t="s">
         <v>69</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="H59" s="38" t="s">
+      <c r="H59" s="35" t="s">
         <v>139</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J59" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="K59" s="37" t="s">
-        <v>278</v>
+        <v>252</v>
+      </c>
+      <c r="J59" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="K59" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L59" s="6" t="e">
         <f>IF(#REF!="",L58,#REF!)</f>
@@ -8998,29 +5999,29 @@
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="56" t="s">
+      <c r="B60" s="45"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="31" t="s">
+      <c r="E60" s="29" t="s">
         <v>70</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H60" s="40" t="s">
+      <c r="H60" s="37" t="s">
         <v>140</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J60" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K60" s="37" t="s">
-        <v>278</v>
+      <c r="J60" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K60" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L60" s="6" t="e">
         <f>IF(#REF!="",#REF!,#REF!)</f>
@@ -9032,29 +6033,27 @@
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="B61" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="C61" s="44"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="31" t="s">
+      <c r="B61" s="45"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="29" t="s">
         <v>71</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="H61" s="40" t="s">
+      <c r="H61" s="37" t="s">
         <v>141</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J61" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K61" s="37" t="s">
-        <v>278</v>
+      <c r="J61" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K61" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L61" s="6" t="e">
         <f>IF(B62="",L60,B62)</f>
@@ -9066,31 +6065,31 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="B62" s="55"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="35" t="s">
+      <c r="B62" s="45"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E62" s="31" t="s">
+      <c r="E62" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="F62" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G62" s="42" t="s">
+      <c r="F62" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="G62" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="H62" s="37" t="s">
+      <c r="H62" s="34" t="s">
         <v>149</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J62" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="K62" s="37" t="s">
-        <v>262</v>
+      <c r="J62" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="K62" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L62" s="6" t="e">
         <f>IF(B63="",L61,B63)</f>
@@ -9102,29 +6101,29 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="B63" s="55"/>
-      <c r="C63" s="44"/>
-      <c r="D63" s="35" t="s">
+      <c r="B63" s="45"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E63" s="30" t="s">
+      <c r="E63" s="28" t="s">
         <v>73</v>
       </c>
       <c r="F63" s="8"/>
-      <c r="G63" s="37" t="s">
+      <c r="G63" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="H63" s="37" t="s">
+      <c r="H63" s="34" t="s">
         <v>125</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J63" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="K63" s="37" t="s">
-        <v>278</v>
+      <c r="J63" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="K63" s="34" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9132,102 +6131,114 @@
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="B64" s="55"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="57" t="s">
+      <c r="B64" s="45"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="E64" s="33" t="s">
+      <c r="E64" s="31" t="s">
         <v>74</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H64" s="37" t="s">
+      <c r="H64" s="34" t="s">
         <v>142</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K64" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="L64" s="6" t="str">
+        <v>284</v>
+      </c>
+      <c r="K64" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="L64" s="6">
         <f>IF(B61="",L63,B61)</f>
-        <v>인게임기능</v>
-      </c>
-    </row>
-    <row r="65" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="55"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="36" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="B65" s="45"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="33" t="s">
         <v>84</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="H65" s="41" t="s">
+      <c r="H65" s="38" t="s">
         <v>143</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J65" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="K65" s="42" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="66" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="55"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="58"/>
+      <c r="J65" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="K65" s="39" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="B66" s="45"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="46"/>
       <c r="E66" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G66" s="36" t="s">
+      <c r="G66" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="H66" s="42" t="s">
+      <c r="H66" s="39" t="s">
         <v>144</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J66" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="K66" s="37" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="C67" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="D67" s="51" t="s">
+      <c r="J66" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="K66" s="34" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="B67" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="C67" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="E67" s="30" t="s">
+      <c r="F67" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="G67" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="H67" s="35" t="s">
         <v>159</v>
-      </c>
-      <c r="H67" s="38" t="s">
-        <v>160</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>13</v>
@@ -9239,91 +6250,103 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="68" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="42"/>
-      <c r="C68" s="53"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="30" t="s">
+    <row r="68" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="B68" s="57"/>
+      <c r="C68" s="61"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F68" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="G68" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F68" s="37" t="s">
+      <c r="H68" s="34" t="s">
         <v>161</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>162</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J68" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="K68" s="37" t="s">
-        <v>278</v>
+      <c r="J68" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="K68" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L68" s="6" t="e">
         <f>IF(B69="",L67,B69)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="69" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="42"/>
-      <c r="C69" s="53"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="31" t="s">
+    <row r="69" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B69" s="57"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F69" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="G69" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F69" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G69" s="8" t="s">
+      <c r="H69" s="35" t="s">
         <v>165</v>
-      </c>
-      <c r="H69" s="38" t="s">
-        <v>166</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J69" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="K69" s="37" t="s">
-        <v>278</v>
+      <c r="J69" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="K69" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L69" s="6" t="e">
         <f>IF(B70="",L68,B70)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="70" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="42"/>
-      <c r="C70" s="54" t="s">
+    <row r="70" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B70" s="57"/>
+      <c r="C70" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="D70" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="D70" s="47" t="s">
+      <c r="E70" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E70" s="30" t="s">
+      <c r="F70" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="F70" s="37" t="s">
+      <c r="G70" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="G70" s="37" t="s">
+      <c r="H70" s="34" t="s">
         <v>172</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>173</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J70" s="37" t="s">
-        <v>292</v>
+      <c r="J70" s="34" t="s">
+        <v>291</v>
       </c>
       <c r="K70" s="8"/>
       <c r="L70" s="6" t="e">
@@ -9331,27 +6354,31 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="71" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="42"/>
-      <c r="C71" s="54"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="31" t="s">
+    <row r="71" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B71" s="57"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F71" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="F71" s="38" t="s">
+      <c r="G71" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="G71" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H71" s="38" t="s">
+      <c r="H71" s="35" t="s">
         <v>125</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J71" s="37" t="s">
-        <v>265</v>
+      <c r="J71" s="34" t="s">
+        <v>264</v>
       </c>
       <c r="K71" s="8"/>
       <c r="L71" s="6" t="e">
@@ -9359,182 +6386,206 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="72" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="42"/>
-      <c r="C72" s="54"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="31" t="s">
+    <row r="72" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B72" s="57"/>
+      <c r="C72" s="59"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="F72" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="F72" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>173</v>
+      <c r="H72" s="34" t="s">
+        <v>172</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J72" s="26" t="s">
-        <v>293</v>
+      <c r="J72" s="24" t="s">
+        <v>292</v>
       </c>
       <c r="K72" s="8"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="42"/>
-      <c r="C73" s="54"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="31" t="s">
+    <row r="73" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B73" s="57"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="F73" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="F73" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H73" s="37" t="s">
+      <c r="H73" s="34" t="s">
         <v>125</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J73" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="K73" s="37" t="s">
-        <v>262</v>
+      <c r="J73" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="K73" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L73" s="6" t="e">
         <f>IF(B74="",L71,B74)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="74" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="42"/>
-      <c r="C74" s="54"/>
-      <c r="D74" s="47" t="s">
+    <row r="74" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B74" s="57"/>
+      <c r="C74" s="59"/>
+      <c r="D74" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="E74" s="31" t="s">
+      <c r="E74" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="F74" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="F74" s="37" t="s">
+      <c r="G74" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="H74" s="34" t="s">
         <v>183</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>184</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J74" s="37" t="s">
+      <c r="J74" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="K74" s="34" t="s">
         <v>294</v>
-      </c>
-      <c r="K74" s="37" t="s">
-        <v>295</v>
       </c>
       <c r="L74" s="6" t="e">
         <f>IF(B75="",L73,B75)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="42"/>
-      <c r="C75" s="54"/>
-      <c r="D75" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="E75" s="31" t="s">
+    <row r="75" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B75" s="57"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E75" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F75" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="F75" s="38" t="s">
+      <c r="G75" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="G75" s="36" t="s">
+      <c r="H75" s="35" t="s">
         <v>187</v>
-      </c>
-      <c r="H75" s="38" t="s">
-        <v>188</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J75" s="37" t="s">
+      <c r="J75" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="K75" s="34" t="s">
         <v>294</v>
-      </c>
-      <c r="K75" s="37" t="s">
-        <v>295</v>
       </c>
       <c r="L75" s="6" t="e">
         <f>IF(B76="",L74,B76)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="76" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="42"/>
-      <c r="C76" s="54"/>
-      <c r="D76" s="47" t="s">
+    <row r="76" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B76" s="57"/>
+      <c r="C76" s="59"/>
+      <c r="D76" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="E76" s="30" t="s">
+      <c r="E76" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F76" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="F76" s="39" t="s">
+      <c r="G76" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="H76" s="34" t="s">
         <v>191</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>192</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J76" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="K76" s="37" t="s">
-        <v>278</v>
+      <c r="J76" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="K76" s="34" t="s">
+        <v>277</v>
       </c>
       <c r="L76" s="6" t="e">
         <f>IF(B77="",L75,B77)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="77" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="42"/>
-      <c r="C77" s="43" t="s">
+    <row r="77" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B77" s="57"/>
+      <c r="C77" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="D77" s="47" t="s">
+      <c r="E77" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="E77" s="31" t="s">
+      <c r="F77" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="G77" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="H77" s="35" t="s">
         <v>198</v>
-      </c>
-      <c r="H77" s="38" t="s">
-        <v>199</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J77" s="37" t="s">
-        <v>296</v>
+      <c r="J77" s="34" t="s">
+        <v>295</v>
       </c>
       <c r="K77" s="8"/>
       <c r="L77" s="6" t="e">
@@ -9542,61 +6593,69 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="78" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="42"/>
-      <c r="C78" s="43"/>
-      <c r="D78" s="47" t="s">
+    <row r="78" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B78" s="57"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="E78" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="E78" s="31" t="s">
+      <c r="F78" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="F78" s="37" t="s">
+      <c r="G78" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G78" s="8" t="s">
+      <c r="H78" s="35" t="s">
         <v>203</v>
-      </c>
-      <c r="H78" s="38" t="s">
-        <v>204</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J78" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="K78" s="37" t="s">
-        <v>262</v>
+      <c r="J78" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="K78" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="L78" s="6" t="e">
         <f>IF(B79="",#REF!,B79)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="79" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="42"/>
-      <c r="C79" s="43"/>
-      <c r="D79" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="E79" s="31" t="s">
+    <row r="79" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B79" s="57"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="F79" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="F79" s="37" t="s">
+      <c r="G79" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="H79" s="35" t="s">
         <v>207</v>
-      </c>
-      <c r="H79" s="38" t="s">
-        <v>208</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J79" s="37" t="s">
-        <v>298</v>
+      <c r="J79" s="34" t="s">
+        <v>297</v>
       </c>
       <c r="K79" s="8"/>
       <c r="L79" s="6" t="e">
@@ -9604,27 +6663,31 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="80" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="42"/>
-      <c r="C80" s="43"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="31" t="s">
+    <row r="80" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B80" s="57"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="F80" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="F80" s="37" t="s">
+      <c r="G80" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="G80" s="42" t="s">
+      <c r="H80" s="34" t="s">
         <v>211</v>
-      </c>
-      <c r="H80" s="37" t="s">
-        <v>212</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J80" s="37" t="s">
-        <v>299</v>
+      <c r="J80" s="34" t="s">
+        <v>298</v>
       </c>
       <c r="K80" s="8"/>
       <c r="L80" s="6" t="e">
@@ -9632,50 +6695,58 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="81" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="42"/>
-      <c r="C81" s="43"/>
-      <c r="D81" s="47"/>
-      <c r="E81" s="30" t="s">
+    <row r="81" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B81" s="57"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="F81" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="F81" s="37" t="s">
+      <c r="G81" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="G81" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="H81" s="37" t="s">
+      <c r="H81" s="34" t="s">
         <v>126</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J81" s="37" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="42"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="47"/>
-      <c r="E82" s="31" t="s">
+      <c r="J81" s="34" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B82" s="57"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="F82" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="F82" s="26" t="s">
+      <c r="G82" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G82" s="8" t="s">
+      <c r="H82" s="34" t="s">
         <v>218</v>
-      </c>
-      <c r="H82" s="37" t="s">
-        <v>219</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J82" s="37" t="s">
-        <v>300</v>
+      <c r="J82" s="34" t="s">
+        <v>299</v>
       </c>
       <c r="K82" s="8"/>
       <c r="L82" s="6">
@@ -9683,73 +6754,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="42"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="47"/>
-      <c r="E83" s="48" t="s">
+    <row r="83" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B83" s="57"/>
+      <c r="C83" s="56"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="F83" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="G83" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F83" s="42" t="s">
-        <v>214</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="H83" s="38" t="s">
+      <c r="H83" s="35" t="s">
         <v>125</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J83" s="42" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="42"/>
-      <c r="C84" s="43"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="30" t="s">
+      <c r="J83" s="39" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B84" s="57"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="F84" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="F84" s="42" t="s">
+      <c r="G84" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="G84" s="36" t="s">
+      <c r="H84" s="39" t="s">
         <v>224</v>
-      </c>
-      <c r="H84" s="42" t="s">
-        <v>225</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J84" s="37" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="85" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="42"/>
-      <c r="C85" s="43"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="31" t="s">
+      <c r="J84" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B85" s="57"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="F85" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="F85" s="37" t="s">
+      <c r="G85" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="G85" s="8" t="s">
+      <c r="H85" s="34" t="s">
         <v>228</v>
-      </c>
-      <c r="H85" s="37" t="s">
-        <v>229</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J85" s="37" t="s">
-        <v>302</v>
+      <c r="J85" s="34" t="s">
+        <v>301</v>
       </c>
       <c r="K85" s="8"/>
       <c r="L85" s="6">
@@ -9757,79 +6840,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="42"/>
-      <c r="C86" s="43"/>
-      <c r="D86" s="47"/>
-      <c r="E86" s="48" t="s">
+    <row r="86" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B86" s="57"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="F86" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="F86" s="42" t="s">
+      <c r="G86" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="G86" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H86" s="38" t="s">
+      <c r="H86" s="35" t="s">
         <v>126</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J86" s="42" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="87" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="42"/>
-      <c r="C87" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="D87" s="50" t="s">
+      <c r="J86" s="39" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B87" s="57"/>
+      <c r="C87" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="D87" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="E87" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="E87" s="30" t="s">
+      <c r="F87" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="F87" s="42" t="s">
+      <c r="G87" s="33" t="s">
         <v>240</v>
       </c>
-      <c r="G87" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="H87" s="42" t="s">
+      <c r="H87" s="39" t="s">
         <v>125</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J87" s="37" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="88" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="42"/>
-      <c r="C88" s="44"/>
-      <c r="D88" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="E88" s="31" t="s">
+      <c r="J87" s="34" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B88" s="57"/>
+      <c r="C88" s="56"/>
+      <c r="D88" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="F88" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="F88" s="37" t="s">
+      <c r="G88" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="G88" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="H88" s="37" t="s">
+      <c r="H88" s="34" t="s">
         <v>125</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J88" s="37" t="s">
-        <v>265</v>
+      <c r="J88" s="34" t="s">
+        <v>264</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88" s="6">
@@ -9837,71 +6932,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="42"/>
-      <c r="C89" s="44"/>
-      <c r="D89" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="E89" s="48" t="s">
+    <row r="89" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B89" s="57"/>
+      <c r="C89" s="56"/>
+      <c r="D89" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E89" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="F89" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="F89" s="42" t="s">
+      <c r="G89" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="H89" s="35" t="s">
         <v>247</v>
-      </c>
-      <c r="H89" s="38" t="s">
-        <v>248</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J89" s="42" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="90" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="42"/>
-      <c r="C90" s="45"/>
-      <c r="D90" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="E90" s="30" t="s">
+      <c r="J89" s="39" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B90" s="57"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="F90" s="42" t="s">
+      <c r="E90" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="F90" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="G90" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="G90" s="36" t="s">
+      <c r="H90" s="39" t="s">
         <v>250</v>
-      </c>
-      <c r="H90" s="42" t="s">
-        <v>251</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J90" s="37" t="s">
-        <v>304</v>
+      <c r="J90" s="34" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="B61:B66"/>
+  <mergeCells count="38">
+    <mergeCell ref="B15:B66"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C31:C48"/>
+    <mergeCell ref="C49:C66"/>
+    <mergeCell ref="B67:B90"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="D79:D86"/>
+    <mergeCell ref="C87:C90"/>
+    <mergeCell ref="C77:C86"/>
+    <mergeCell ref="C70:C76"/>
+    <mergeCell ref="C67:C69"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="D64:D66"/>
@@ -9910,938 +7013,112 @@
     <mergeCell ref="D38:D39"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="D24:D25"/>
-    <mergeCell ref="B15:B59"/>
     <mergeCell ref="C15:C30"/>
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="C33:C48"/>
     <mergeCell ref="D34:D35"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D52:D53"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1">
-    <cfRule type="containsBlanks" dxfId="309" priority="343">
+    <cfRule type="containsBlanks" dxfId="22" priority="343">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="308" priority="346" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="21" priority="346" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="307" priority="350" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="20" priority="350" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="306" priority="354" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="19" priority="354" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="305" priority="358" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="18" priority="358" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="304" priority="362" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="17" priority="362" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(A1))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="containsText" dxfId="303" priority="349" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="16" priority="349" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="302" priority="353" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="15" priority="353" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="301" priority="357" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="14" priority="357" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="300" priority="361" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="13" priority="361" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2 I23:I29 I4:I21">
-    <cfRule type="containsBlanks" dxfId="257" priority="344">
-      <formula>LEN(TRIM(I1))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="256" priority="363" operator="containsText" text="N/T">
+  <conditionalFormatting sqref="I1:I2">
+    <cfRule type="containsText" dxfId="12" priority="363" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2 I23:I29 I4:I21">
-    <cfRule type="containsText" dxfId="255" priority="347" operator="containsText" text="Pass">
+  <conditionalFormatting sqref="I1:I90">
+    <cfRule type="containsBlanks" dxfId="11" priority="1">
+      <formula>LEN(TRIM(I1))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I90">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="254" priority="351" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="253" priority="355" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="252" priority="359" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:I37 I44 I46 I39">
-    <cfRule type="containsBlanks" dxfId="299" priority="295">
-      <formula>LEN(TRIM(I33))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="298" priority="296" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="297" priority="297" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="296" priority="298" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="295" priority="299" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I33))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="294" priority="300" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I51:I54 I57 I62 I64">
-    <cfRule type="containsBlanks" dxfId="293" priority="277">
-      <formula>LEN(TRIM(I51))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="292" priority="278" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I51))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="291" priority="279" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I51))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="290" priority="280" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I51))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="289" priority="281" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I51))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="288" priority="282" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I51))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I70:I73 I76:I82">
-    <cfRule type="containsBlanks" dxfId="287" priority="265">
-      <formula>LEN(TRIM(I70))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="286" priority="266" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I70))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="285" priority="267" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I70))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="284" priority="268" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I70))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="283" priority="269" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I70))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="282" priority="270" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I70))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I85">
-    <cfRule type="containsBlanks" dxfId="281" priority="253">
-      <formula>LEN(TRIM(I85))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="280" priority="254" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I85))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="279" priority="255" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I85))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="278" priority="256" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I85))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="277" priority="257" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I85))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="276" priority="258" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I85))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I87:I88">
-    <cfRule type="containsBlanks" dxfId="275" priority="241">
-      <formula>LEN(TRIM(I87))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="274" priority="242" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I87))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="273" priority="243" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I87))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="272" priority="244" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I87))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="271" priority="245" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I87))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="270" priority="246" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I87))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I90">
-    <cfRule type="containsBlanks" dxfId="269" priority="235">
-      <formula>LEN(TRIM(I90))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="268" priority="236" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I90))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="267" priority="237" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I90))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="266" priority="238" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I90))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="265" priority="239" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I90))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="264" priority="240" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I90))))</formula>
+  <conditionalFormatting sqref="I3:I90">
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="containsBlanks" dxfId="263" priority="345">
+    <cfRule type="containsBlanks" dxfId="5" priority="345">
       <formula>LEN(TRIM(J1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="262" priority="348" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="4" priority="348" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="261" priority="352" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="3" priority="352" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="260" priority="356" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="2" priority="356" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="259" priority="360" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="1" priority="360" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="258" priority="364" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="0" priority="364" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(J1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I30">
-    <cfRule type="containsBlanks" dxfId="251" priority="229">
-      <formula>LEN(TRIM(I30))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="250" priority="234" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I30">
-    <cfRule type="containsText" dxfId="249" priority="230" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I30))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="248" priority="231" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I30))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="247" priority="232" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I30))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="233" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I32">
-    <cfRule type="containsBlanks" dxfId="245" priority="223">
-      <formula>LEN(TRIM(I32))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="244" priority="228" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I32">
-    <cfRule type="containsText" dxfId="243" priority="224" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="242" priority="225" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="241" priority="226" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I32))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="240" priority="227" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I42">
-    <cfRule type="containsBlanks" dxfId="227" priority="211">
-      <formula>LEN(TRIM(I42))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="226" priority="216" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I42))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I42">
-    <cfRule type="containsText" dxfId="225" priority="212" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I42))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="224" priority="213" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I42))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="223" priority="214" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I42))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="215" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I42))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43">
-    <cfRule type="containsBlanks" dxfId="215" priority="199">
-      <formula>LEN(TRIM(I43))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="204" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43">
-    <cfRule type="containsText" dxfId="213" priority="200" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I43))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="212" priority="201" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I43))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="202" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I43))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="210" priority="203" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45">
-    <cfRule type="containsBlanks" dxfId="209" priority="193">
-      <formula>LEN(TRIM(I45))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="208" priority="198" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I45))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45">
-    <cfRule type="containsText" dxfId="207" priority="194" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I45))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="206" priority="195" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I45))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="205" priority="196" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I45))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="204" priority="197" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I45))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I48">
-    <cfRule type="containsBlanks" dxfId="203" priority="187">
-      <formula>LEN(TRIM(I48))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="202" priority="192" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I48))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I48">
-    <cfRule type="containsText" dxfId="201" priority="188" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I48))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="200" priority="189" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I48))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="199" priority="190" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I48))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="191" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I48))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I55">
-    <cfRule type="containsBlanks" dxfId="197" priority="181">
-      <formula>LEN(TRIM(I55))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="196" priority="186" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I55))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I55">
-    <cfRule type="containsText" dxfId="195" priority="182" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I55))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="194" priority="183" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I55))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="193" priority="184" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I55))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="192" priority="185" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I55))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I61">
-    <cfRule type="containsBlanks" dxfId="179" priority="163">
-      <formula>LEN(TRIM(I61))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="178" priority="168" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I61))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I61">
-    <cfRule type="containsText" dxfId="177" priority="164" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I61))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="176" priority="165" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I61))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="175" priority="166" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I61))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="174" priority="167" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I61))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I60">
-    <cfRule type="containsBlanks" dxfId="173" priority="157">
-      <formula>LEN(TRIM(I60))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="172" priority="162" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I60))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I60">
-    <cfRule type="containsText" dxfId="171" priority="158" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I60))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="170" priority="159" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I60))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="169" priority="160" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I60))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="168" priority="161" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I60))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I63">
-    <cfRule type="containsBlanks" dxfId="167" priority="151">
-      <formula>LEN(TRIM(I63))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="166" priority="156" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I63))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I63">
-    <cfRule type="containsText" dxfId="165" priority="152" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I63))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="164" priority="153" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I63))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="163" priority="154" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I63))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="162" priority="155" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I63))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I66">
-    <cfRule type="containsBlanks" dxfId="161" priority="145">
-      <formula>LEN(TRIM(I66))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="160" priority="150" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I66))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I66">
-    <cfRule type="containsText" dxfId="159" priority="146" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I66))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="158" priority="147" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I66))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="157" priority="148" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I66))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="156" priority="149" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I66))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I69">
-    <cfRule type="containsBlanks" dxfId="155" priority="139">
-      <formula>LEN(TRIM(I69))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="154" priority="144" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I69))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I69">
-    <cfRule type="containsText" dxfId="153" priority="140" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I69))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="152" priority="141" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I69))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="151" priority="142" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I69))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="150" priority="143" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I69))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I68">
-    <cfRule type="containsBlanks" dxfId="149" priority="133">
-      <formula>LEN(TRIM(I68))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="148" priority="138" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I68))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I68">
-    <cfRule type="containsText" dxfId="147" priority="134" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="146" priority="135" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="145" priority="136" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I68))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="144" priority="137" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I68))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I75">
-    <cfRule type="containsBlanks" dxfId="143" priority="127">
-      <formula>LEN(TRIM(I75))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="142" priority="132" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I75))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I75">
-    <cfRule type="containsText" dxfId="141" priority="128" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I75))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="129" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I75))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="139" priority="130" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I75))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="138" priority="131" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I75))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I74">
-    <cfRule type="containsBlanks" dxfId="137" priority="121">
-      <formula>LEN(TRIM(I74))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="136" priority="126" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I74))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I74">
-    <cfRule type="containsText" dxfId="135" priority="122" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I74))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="134" priority="123" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I74))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="133" priority="124" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I74))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="132" priority="125" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I74))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I41">
-    <cfRule type="containsBlanks" dxfId="113" priority="109">
-      <formula>LEN(TRIM(I41))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="114" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I41))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I41">
-    <cfRule type="containsText" dxfId="111" priority="110" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I41))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="111" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I41))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="109" priority="112" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I41))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="108" priority="113" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I41))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I59">
-    <cfRule type="containsBlanks" dxfId="101" priority="97">
-      <formula>LEN(TRIM(I59))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="102" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I59))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I59">
-    <cfRule type="containsText" dxfId="99" priority="98" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I59))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="99" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I59))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="100" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I59))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="101" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I59))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I58">
-    <cfRule type="containsBlanks" dxfId="95" priority="91">
-      <formula>LEN(TRIM(I58))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="96" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I58))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I58">
-    <cfRule type="containsText" dxfId="93" priority="92" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I58))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="93" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I58))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="94" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I58))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="95" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I58))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40">
-    <cfRule type="containsBlanks" dxfId="89" priority="85">
-      <formula>LEN(TRIM(I40))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="90" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I40))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40">
-    <cfRule type="containsText" dxfId="87" priority="86" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I40))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="87" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I40))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="88" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I40))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="89" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I40))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22">
-    <cfRule type="containsBlanks" dxfId="83" priority="79">
-      <formula>LEN(TRIM(I22))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="84" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22">
-    <cfRule type="containsText" dxfId="81" priority="80" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I22))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="81" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I22))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="82" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I22))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="83" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31">
-    <cfRule type="containsBlanks" dxfId="77" priority="73">
-      <formula>LEN(TRIM(I31))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="78" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="75" priority="74" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I31))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="75" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I31))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="76" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I31))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="77" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I38">
-    <cfRule type="containsBlanks" dxfId="71" priority="67">
-      <formula>LEN(TRIM(I38))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="72" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="69" priority="68" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I38))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="69" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I38))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="70" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I38))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="71" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I47">
-    <cfRule type="containsBlanks" dxfId="65" priority="61">
-      <formula>LEN(TRIM(I47))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="66" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I47))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I47">
-    <cfRule type="containsText" dxfId="63" priority="62" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I47))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="63" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I47))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="64" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I47))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="65" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I47))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49">
-    <cfRule type="containsBlanks" dxfId="59" priority="55">
-      <formula>LEN(TRIM(I49))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="60" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49">
-    <cfRule type="containsText" dxfId="57" priority="56" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I49))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="57" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I49))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="58" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I49))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="59" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I50">
-    <cfRule type="containsBlanks" dxfId="53" priority="49">
-      <formula>LEN(TRIM(I50))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="54" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I50">
-    <cfRule type="containsText" dxfId="51" priority="50" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I50))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="51" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I50))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="52" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I50))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="53" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I56">
-    <cfRule type="containsBlanks" dxfId="47" priority="43">
-      <formula>LEN(TRIM(I56))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="48" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I56))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I56">
-    <cfRule type="containsText" dxfId="45" priority="44" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I56))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="45" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I56))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="46" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I56))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="47" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I56))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I65">
-    <cfRule type="containsBlanks" dxfId="41" priority="37">
-      <formula>LEN(TRIM(I65))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="42" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I65))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I65">
-    <cfRule type="containsText" dxfId="39" priority="38" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I65))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="39" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I65))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="40" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I65))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="41" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I65))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I67">
-    <cfRule type="containsBlanks" dxfId="35" priority="31">
-      <formula>LEN(TRIM(I67))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I67))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I67">
-    <cfRule type="containsText" dxfId="33" priority="32" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I67))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="33" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I67))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="34" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I67))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="35" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I67))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I86">
-    <cfRule type="containsBlanks" dxfId="29" priority="25">
-      <formula>LEN(TRIM(I86))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I86))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I86">
-    <cfRule type="containsText" dxfId="27" priority="26" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I86))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I86))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I86))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="29" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I86))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I84">
-    <cfRule type="containsBlanks" dxfId="23" priority="19">
-      <formula>LEN(TRIM(I84))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I84))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I84">
-    <cfRule type="containsText" dxfId="21" priority="20" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I84))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I84))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="22" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I84))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I84))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I83">
-    <cfRule type="containsBlanks" dxfId="17" priority="13">
-      <formula>LEN(TRIM(I83))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I83))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I83">
-    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I83))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I83))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I83))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I83))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I89">
-    <cfRule type="containsBlanks" dxfId="11" priority="7">
-      <formula>LEN(TRIM(I89))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I89))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I89">
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I89))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I89))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I89))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I89))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsBlanks" dxfId="5" priority="1">
-      <formula>LEN(TRIM(I3))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I3))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I3))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I3))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="L19" evalError="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -10851,7 +7128,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -10903,20 +7180,17 @@
         <v>11</v>
       </c>
       <c r="B3" s="12">
-        <f>COUNTIF(TestCase!L:L,A3)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="13">
-        <f t="shared" ref="C3:C5" si="0">IFERROR(B3/$B$6,0)</f>
-        <v>0.54545454545454541</v>
+        <f>IFERROR(B3/$B$7,0)</f>
+        <v>0.10112359550561797</v>
       </c>
       <c r="D3" s="12">
-        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A3)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="12">
-        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;E$2&amp;"*",TestCase!$L:$L,$A3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="12">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;F$2&amp;"*",TestCase!$L:$L,$A3)</f>
@@ -10931,12 +7205,11 @@
         <v>1</v>
       </c>
       <c r="I3" s="12">
-        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;I$2&amp;"*",TestCase!$L:$L,$A3)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J3" s="15">
         <f>I3/B3</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10948,8 +7221,8 @@
         <v>4</v>
       </c>
       <c r="C4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.36363636363636365</v>
+        <f>IFERROR(B4/$B$7,0)</f>
+        <v>4.49438202247191E-2</v>
       </c>
       <c r="D4" s="12">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A4)</f>
@@ -10972,11 +7245,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="14">
-        <f t="shared" ref="I4:I5" si="1">SUM(D4:H4)</f>
+        <f t="shared" ref="I4:I5" si="0">SUM(D4:H4)</f>
         <v>4</v>
       </c>
       <c r="J4" s="15">
-        <f t="shared" ref="J4:J5" si="2">I4/B4</f>
+        <f t="shared" ref="J4:J5" si="1">I4/B4</f>
         <v>1</v>
       </c>
     </row>
@@ -10985,111 +7258,145 @@
         <v>34</v>
       </c>
       <c r="B5" s="12">
-        <f>COUNTIF(TestCase!L:L,A5)</f>
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="C5" s="13">
-        <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
+        <f>IFERROR(B5/$B$7,0)</f>
+        <v>0.5842696629213483</v>
       </c>
       <c r="D5" s="12">
-        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A5)</f>
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;E$2&amp;"*",TestCase!$L:$L,$A5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="12">
-        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;F$2&amp;"*",TestCase!$L:$L,$A5)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5" s="12">
-        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;G$2&amp;"*",TestCase!$L:$L,$A5)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="12">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;H$2&amp;"*",TestCase!$L:$L,$A5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="14">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="J5" s="15">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J5" s="15">
-        <f t="shared" si="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="12">
+        <v>24</v>
+      </c>
+      <c r="C6" s="13">
+        <f>IFERROR(B6/$B$7,0)</f>
+        <v>0.2696629213483146</v>
+      </c>
+      <c r="D6" s="12">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12">
+        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;E$2&amp;"*",TestCase!$L:$L,$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;F$2&amp;"*",TestCase!$L:$L,$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <f>COUNTIFS(TestCase!$I:$I,"*"&amp;G$2&amp;"*",TestCase!$L:$L,$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>4</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="shared" ref="I6" si="2">SUM(D6:H6)</f>
+        <v>24</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" ref="J6" si="3">I6/B6</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="16">
-        <f t="shared" ref="B6:H6" si="3">SUM(B3:B5)</f>
-        <v>11</v>
-      </c>
-      <c r="C6" s="17">
-        <f>SUM(C3:C5)</f>
-        <v>1</v>
-      </c>
-      <c r="D6" s="14">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="E6" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="14">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="14">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="H6" s="14">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I6" s="14">
-        <f>SUM(I3:I5)</f>
-        <v>5</v>
-      </c>
-      <c r="J6" s="14"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="66">
+        <f>SUM(B3:B6)</f>
+        <v>89</v>
+      </c>
+      <c r="C7" s="68">
+        <f>SUM(C3:C6)/SUM($C$3:$C$6)</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="67">
+        <f>SUM(D3:D6)</f>
+        <v>58</v>
+      </c>
+      <c r="E7" s="67">
+        <f>SUM(E3:E6)</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="67">
+        <f>SUM(F3:F6)</f>
+        <v>19</v>
+      </c>
+      <c r="G7" s="67">
+        <f>SUM(G3:G6)</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="67">
+        <f>SUM(H3:H6)</f>
+        <v>6</v>
+      </c>
+      <c r="I7" s="67">
+        <f>SUM(I3:I6)</f>
+        <v>89</v>
+      </c>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="15">
-        <f t="shared" ref="D7:I7" si="4">D6/$B6</f>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="E7" s="15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <f t="shared" si="4"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="G7" s="15">
-        <f t="shared" si="4"/>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="H7" s="15">
-        <f t="shared" si="4"/>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="I7" s="15">
-        <f t="shared" si="4"/>
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="J7" s="14"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="15">
+        <f>D7/$B7</f>
+        <v>0.651685393258427</v>
+      </c>
+      <c r="E8" s="15">
+        <f>E7/$B7</f>
+        <v>1.1235955056179775E-2</v>
+      </c>
+      <c r="F8" s="15">
+        <f>F7/$B7</f>
+        <v>0.21348314606741572</v>
+      </c>
+      <c r="G8" s="15">
+        <f>G7/$B7</f>
+        <v>5.6179775280898875E-2</v>
+      </c>
+      <c r="H8" s="15">
+        <f>H7/$B7</f>
+        <v>6.741573033707865E-2</v>
+      </c>
+      <c r="I8" s="15">
+        <f>I7/$B7</f>
+        <v>1</v>
+      </c>
+      <c r="J8" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
